--- a/SGC-CKN/Excel/f20164b3-007a-492e-b612-f0a35b854248_Thi_công_cọc_khoan_nhồi_CT-02_D800_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/f20164b3-007a-492e-b612-f0a35b854248_Thi_công_cọc_khoan_nhồi_CT-02_D800_14-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>CT-02</t>
+    <t>P7-157</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/f20164b3-007a-492e-b612-f0a35b854248_Thi_công_cọc_khoan_nhồi_CT-02_D800_14-03-2026.xlsx
+++ b/SGC-CKN/Excel/f20164b3-007a-492e-b612-f0a35b854248_Thi_công_cọc_khoan_nhồi_CT-02_D800_14-03-2026.xlsx
@@ -98,7 +98,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">08:00
+    <t xml:space="preserve">08:40
 14/03/2026</t>
   </si>
   <si>
@@ -119,7 +119,7 @@
 14/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">09:55
+    <t xml:space="preserve">09:05
 14/03/2026</t>
   </si>
   <si>
@@ -147,7 +147,7 @@
 14/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">11:20
+    <t xml:space="preserve">11:10
 14/03/2026</t>
   </si>
   <si>
@@ -157,7 +157,7 @@
     <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">11:21
+    <t xml:space="preserve">11:11
 14/03/2026</t>
   </si>
   <si>
@@ -175,7 +175,7 @@
 14/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">13:46
+    <t xml:space="preserve">13:44
 14/03/2026</t>
   </si>
   <si>
@@ -185,7 +185,7 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">13:47
+    <t xml:space="preserve">13:45
 14/03/2026</t>
   </si>
   <si>
@@ -203,7 +203,7 @@
 14/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">14:42
+    <t xml:space="preserve">14:32
 14/03/2026</t>
   </si>
   <si>
@@ -213,7 +213,7 @@
     <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">14:43
+    <t xml:space="preserve">14:35
 14/03/2026</t>
   </si>
   <si>
@@ -231,7 +231,7 @@
 14/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16:55
+    <t xml:space="preserve">15:55
 14/03/2026</t>
   </si>
   <si>
@@ -269,7 +269,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -352,12 +352,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -368,7 +362,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,11 +401,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
@@ -423,6 +412,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -448,11 +442,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -548,7 +537,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -583,35 +572,35 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -658,16 +647,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1253,19 +1239,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.53</v>
+        <v>-5.53</v>
       </c>
       <c r="G11" s="5">
         <v>-6.94</v>
       </c>
       <c r="H11" s="5">
-        <v>0.92</v>
+        <v>0.25</v>
       </c>
       <c r="I11" s="5">
-        <v>6.41</v>
+        <v>1.41</v>
       </c>
       <c r="J11" s="8">
-        <v>6.99</v>
+        <v>5.64</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1294,120 +1280,120 @@
         <v>-9.04</v>
       </c>
       <c r="H12" s="9">
-        <v>0.98</v>
+        <v>0.15</v>
       </c>
       <c r="I12" s="9">
         <v>2.1</v>
       </c>
-      <c r="J12" s="12">
-        <v>2.14</v>
+      <c r="J12" s="8">
+        <v>14</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-9.04</v>
       </c>
-      <c r="G13" s="13">
-        <v>-13.24</v>
-      </c>
-      <c r="H13" s="13">
+      <c r="G13" s="12">
+        <v>-17.24</v>
+      </c>
+      <c r="H13" s="12">
         <v>1.4</v>
       </c>
-      <c r="I13" s="13">
-        <v>4.2</v>
-      </c>
-      <c r="J13" s="12">
-        <v>3</v>
-      </c>
-      <c r="K13" s="14" t="s">
+      <c r="I13" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>5.86</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="16">
-        <v>-13.24</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="15">
+        <v>-17.24</v>
+      </c>
+      <c r="G14" s="15">
         <v>-21.54</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
+        <v>0.65</v>
+      </c>
+      <c r="I14" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="8">
+        <v>6.62</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="18">
+        <v>-21.54</v>
+      </c>
+      <c r="G15" s="18">
+        <v>-25.54</v>
+      </c>
+      <c r="H15" s="18">
         <v>0.82</v>
       </c>
-      <c r="I14" s="16">
-        <v>8.3</v>
-      </c>
-      <c r="J14" s="8">
-        <v>10.16</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="19">
-        <v>-21.54</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-29.74</v>
-      </c>
-      <c r="H15" s="19">
-        <v>0.65</v>
-      </c>
-      <c r="I15" s="19">
-        <v>8.2</v>
-      </c>
-      <c r="J15" s="8">
-        <v>12.62</v>
-      </c>
-      <c r="K15" s="20" t="s">
+      <c r="I15" s="18">
+        <v>4</v>
+      </c>
+      <c r="J15" s="21">
+        <v>4.9</v>
+      </c>
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1428,19 +1414,19 @@
         <v>50</v>
       </c>
       <c r="F16" s="22">
-        <v>-29.74</v>
+        <v>-25.54</v>
       </c>
       <c r="G16" s="22">
         <v>-35.64</v>
       </c>
       <c r="H16" s="22">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="I16" s="22">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="J16" s="8">
-        <v>7.7</v>
+        <v>13.77</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1469,13 +1455,13 @@
         <v>-37.85</v>
       </c>
       <c r="H17" s="25">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="I17" s="25">
         <v>2.21</v>
       </c>
       <c r="J17" s="8">
-        <v>6.03</v>
+        <v>5.53</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1504,13 +1490,13 @@
         <v>-39.5</v>
       </c>
       <c r="H18" s="28">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="I18" s="28">
         <v>1.65</v>
       </c>
-      <c r="J18" s="12">
-        <v>3.09</v>
+      <c r="J18" s="21">
+        <v>4.5</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1539,13 +1525,13 @@
         <v>-44.05</v>
       </c>
       <c r="H19" s="31">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="I19" s="31">
         <v>4.55</v>
       </c>
-      <c r="J19" s="12">
-        <v>4.87</v>
+      <c r="J19" s="21">
+        <v>4.27</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1574,32 +1560,32 @@
         <v>-44.9</v>
       </c>
       <c r="H20" s="34">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="I20" s="34">
         <v>0.85</v>
       </c>
-      <c r="J20" s="37">
-        <v>0.68</v>
+      <c r="J20" s="21">
+        <v>3.4</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1735,19 +1721,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.53</v>
+        <v>-5.53</v>
       </c>
       <c r="F2" s="5">
         <v>-6.94</v>
       </c>
       <c r="G2" s="5">
-        <v>0.92</v>
+        <v>0.25</v>
       </c>
       <c r="H2" s="5">
-        <v>6.41</v>
+        <v>1.41</v>
       </c>
       <c r="I2" s="8">
-        <v>6.99</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1770,100 +1756,100 @@
         <v>-9.04</v>
       </c>
       <c r="G3" s="9">
-        <v>0.98</v>
+        <v>0.15</v>
       </c>
       <c r="H3" s="9">
         <v>2.1</v>
       </c>
-      <c r="I3" s="12">
-        <v>2.14</v>
+      <c r="I3" s="8">
+        <v>14</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-9.04</v>
       </c>
-      <c r="F4" s="13">
-        <v>-13.24</v>
-      </c>
-      <c r="G4" s="13">
+      <c r="F4" s="12">
+        <v>-17.24</v>
+      </c>
+      <c r="G4" s="12">
         <v>1.4</v>
       </c>
-      <c r="H4" s="13">
-        <v>4.2</v>
-      </c>
-      <c r="I4" s="12">
-        <v>3</v>
+      <c r="H4" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>5.86</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-13.24</v>
-      </c>
-      <c r="F5" s="16">
+      <c r="E5" s="15">
+        <v>-17.24</v>
+      </c>
+      <c r="F5" s="15">
         <v>-21.54</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
+        <v>0.65</v>
+      </c>
+      <c r="H5" s="15">
+        <v>4.3</v>
+      </c>
+      <c r="I5" s="8">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="18">
+        <v>1</v>
+      </c>
+      <c r="E6" s="18">
+        <v>-21.54</v>
+      </c>
+      <c r="F6" s="18">
+        <v>-25.54</v>
+      </c>
+      <c r="G6" s="18">
         <v>0.82</v>
       </c>
-      <c r="H5" s="16">
-        <v>8.3</v>
-      </c>
-      <c r="I5" s="8">
-        <v>10.16</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="19">
-        <v>1</v>
-      </c>
-      <c r="E6" s="19">
-        <v>-21.54</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-29.74</v>
-      </c>
-      <c r="G6" s="19">
-        <v>0.65</v>
-      </c>
-      <c r="H6" s="19">
-        <v>8.2</v>
-      </c>
-      <c r="I6" s="8">
-        <v>12.62</v>
+      <c r="H6" s="18">
+        <v>4</v>
+      </c>
+      <c r="I6" s="21">
+        <v>4.9</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1880,19 +1866,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-29.74</v>
+        <v>-25.54</v>
       </c>
       <c r="F7" s="22">
         <v>-35.64</v>
       </c>
       <c r="G7" s="22">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="H7" s="22">
-        <v>5.9</v>
+        <v>10.1</v>
       </c>
       <c r="I7" s="8">
-        <v>7.7</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1915,13 +1901,13 @@
         <v>-37.85</v>
       </c>
       <c r="G8" s="25">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H8" s="25">
         <v>2.21</v>
       </c>
       <c r="I8" s="8">
-        <v>6.03</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1944,13 +1930,13 @@
         <v>-39.5</v>
       </c>
       <c r="G9" s="28">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="H9" s="28">
         <v>1.65</v>
       </c>
-      <c r="I9" s="12">
-        <v>3.09</v>
+      <c r="I9" s="21">
+        <v>4.5</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1973,13 +1959,13 @@
         <v>-44.05</v>
       </c>
       <c r="G10" s="31">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="H10" s="31">
         <v>4.55</v>
       </c>
-      <c r="I10" s="12">
-        <v>4.87</v>
+      <c r="I10" s="21">
+        <v>4.27</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2002,42 +1988,42 @@
         <v>-44.9</v>
       </c>
       <c r="G11" s="34">
-        <v>1.25</v>
+        <v>0.25</v>
       </c>
       <c r="H11" s="34">
         <v>0.85</v>
       </c>
-      <c r="I11" s="37">
-        <v>0.68</v>
+      <c r="I11" s="21">
+        <v>3.4</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
-        <v>-0.53</v>
-      </c>
-      <c r="F12" s="40">
+      <c r="E12" s="39">
+        <v>-5.53</v>
+      </c>
+      <c r="F12" s="39">
         <v>-44.9</v>
       </c>
-      <c r="G12" s="40">
-        <v>8.62</v>
-      </c>
-      <c r="H12" s="40">
-        <v>44.37</v>
-      </c>
-      <c r="I12" s="40">
-        <v>5.15</v>
+      <c r="G12" s="39">
+        <v>6.08</v>
+      </c>
+      <c r="H12" s="39">
+        <v>39.37</v>
+      </c>
+      <c r="I12" s="39">
+        <v>6.47</v>
       </c>
     </row>
   </sheetData>
